--- a/Envio de Invitaciones.xlsx
+++ b/Envio de Invitaciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vikthor09\Documents\Invitacion XV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E28AFA2-F864-44E9-B6B7-4E3C3FF3F588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31EBED5-5BBE-4971-B016-7FDA1C3B81E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{63E471A0-DCBF-4325-8653-7C36EBD83C5B}"/>
+    <workbookView xWindow="4875" yWindow="2895" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{63E471A0-DCBF-4325-8653-7C36EBD83C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t>FAMILIA</t>
   </si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>Arellano Vera</t>
-  </si>
-  <si>
-    <t>castillo</t>
   </si>
 </sst>
 </file>
@@ -562,7 +559,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E910A99-7A52-4365-AC7B-EF9714532458}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -598,8 +595,8 @@
         <v>4</v>
       </c>
       <c r="C2" t="str">
-        <f>"https://cyber911zona.github.io/cenicienta/?n=Familia_"&amp;SUBSTITUTE(A2," ","_")&amp;"&amp;p="&amp;B2</f>
-        <v>https://cyber911zona.github.io/cenicienta/?n=Familia_Arellano_Vera&amp;p=4</v>
+        <f>"https://cyber911zona.github.io/invitacionXV2/?n=Familia_"&amp;SUBSTITUTE(A2," ","_")&amp;"&amp;p="&amp;B2</f>
+        <v>https://cyber911zona.github.io/invitacionXV2/?n=Familia_Arellano_Vera&amp;p=4</v>
       </c>
       <c r="D2" s="1" t="str">
         <f>HYPERLINK("https://wa.me/"&amp;E2&amp;"?text=%20"&amp;SUBSTITUTE(C2, "&amp;", "%26"), "ENVIAR POR WHATSAPP")</f>
@@ -617,11 +614,11 @@
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3:C5" si="0">"https://cyber911zona.github.io/cenicienta/?n=Familia_"&amp;SUBSTITUTE(A3," ","_")&amp;"&amp;p="&amp;B3</f>
-        <v>https://cyber911zona.github.io/cenicienta/?n=Familia_Vera&amp;p=2</v>
+        <f>"https://cyber911zona.github.io/invitacionXV2/?n=Familia_"&amp;SUBSTITUTE(A3," ","_")&amp;"&amp;p="&amp;B3</f>
+        <v>https://cyber911zona.github.io/invitacionXV2/?n=Familia_Vera&amp;p=2</v>
       </c>
       <c r="D3" s="1" t="str">
-        <f t="shared" ref="D3:D5" si="1">HYPERLINK("https://wa.me/"&amp;E3&amp;"?text=%20"&amp;SUBSTITUTE(C3, "&amp;", "%26"), "ENVIAR POR WHATSAPP")</f>
+        <f t="shared" ref="D3:D5" si="0">HYPERLINK("https://wa.me/"&amp;E3&amp;"?text=%20"&amp;SUBSTITUTE(C3, "&amp;", "%26"), "ENVIAR POR WHATSAPP")</f>
         <v>ENVIAR POR WHATSAPP</v>
       </c>
       <c r="E3" s="2">
@@ -636,11 +633,11 @@
         <v>3</v>
       </c>
       <c r="C4" t="str">
+        <f t="shared" ref="C4:C5" si="1">"https://cyber911zona.github.io/invitacionXV2/?n=Familia_"&amp;SUBSTITUTE(A4," ","_")&amp;"&amp;p="&amp;B4</f>
+        <v>https://cyber911zona.github.io/invitacionXV2/?n=Familia_Garcia&amp;p=3</v>
+      </c>
+      <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>https://cyber911zona.github.io/cenicienta/?n=Familia_Garcia&amp;p=3</v>
-      </c>
-      <c r="D4" s="1" t="str">
-        <f t="shared" si="1"/>
         <v>ENVIAR POR WHATSAPP</v>
       </c>
       <c r="E4" s="2">
@@ -655,33 +652,14 @@
         <v>4</v>
       </c>
       <c r="C5" t="str">
+        <f t="shared" si="1"/>
+        <v>https://cyber911zona.github.io/invitacionXV2/?n=Familia_Hernandez&amp;p=4</v>
+      </c>
+      <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>https://cyber911zona.github.io/cenicienta/?n=Familia_Hernandez&amp;p=4</v>
-      </c>
-      <c r="D5" s="1" t="str">
-        <f t="shared" si="1"/>
         <v>ENVIAR POR WHATSAPP</v>
       </c>
       <c r="E5" s="2">
-        <v>522722659554</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="4">
-        <v>23</v>
-      </c>
-      <c r="C6" t="str">
-        <f>"https://cyber911zona.github.io/cenicienta3/?n=Familia_"&amp;SUBSTITUTE(A6," ","_")&amp;"&amp;p="&amp;B6</f>
-        <v>https://cyber911zona.github.io/cenicienta3/?n=Familia_castillo&amp;p=23</v>
-      </c>
-      <c r="D6" s="1" t="str">
-        <f t="shared" ref="D6" si="2">HYPERLINK("https://wa.me/"&amp;E6&amp;"?text=%20"&amp;SUBSTITUTE(C6, "&amp;", "%26"), "ENVIAR POR WHATSAPP")</f>
-        <v>ENVIAR POR WHATSAPP</v>
-      </c>
-      <c r="E6" s="2">
         <v>522722659554</v>
       </c>
     </row>
